--- a/src/New-release/Figure7.xlsx
+++ b/src/New-release/Figure7.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\visualisations\dvc3400-3499\dvc3420-productivity-flash\fig7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2025 IndQ2 - 2025 WEQ3/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F8136E-062E-466C-985B-2838ABE45262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5562CA3-828E-4E9B-89F4-1165ABD100D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="672" yWindow="696" windowWidth="19116" windowHeight="10092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="datadownload" sheetId="2" r:id="rId1"/>
+    <sheet name="Data for Dataviz" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
-    <t>Figure 7: In 2025Q2 the IT industry saw output per hour grow by 36.7% in comparison with 2019 average due to a large increase in GVA (up from 29.2% a quarter ago and before Bluebook 25 revisions)</t>
+    <t>Figure 7: In 2025Q2 the IT industry saw output per hour grow by 36.7% in comparison with its 2019 average due to a large increase in GVA (up from 29.2% a quarter ago and before Bluebook 25 revisions)</t>
   </si>
   <si>
     <t xml:space="preserve">Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 2 (Apr to Jun) 2025 compared with 2019 average, percentage change, UK </t>
@@ -129,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,7 +140,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -510,31 +509,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F044E81-6507-406E-A706-F956F5590C89}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.15"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -542,7 +541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -556,7 +555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -572,7 +571,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -580,15 +579,15 @@
         <v>5.0226191857093198E-2</v>
       </c>
       <c r="C9" s="3">
-        <v>-0.13461631973292701</v>
+        <v>-0.13596610053049299</v>
       </c>
       <c r="D9" s="3">
-        <v>0.21359602197833699</v>
+        <v>0.215491883480386</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -596,15 +595,15 @@
         <v>-0.39293214406683902</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.253262047021522</v>
+        <v>-0.25321468064623004</v>
       </c>
       <c r="D10" s="3">
-        <v>-0.187040308435136</v>
+        <v>-0.18709187205435801</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -612,15 +611,15 @@
         <v>4.2571024223576802E-2</v>
       </c>
       <c r="C11" s="3">
-        <v>-4.7606179518868197E-2</v>
+        <v>-4.7980577264259396E-2</v>
       </c>
       <c r="D11" s="3">
-        <v>9.4684784595608903E-2</v>
+        <v>9.5115287908334512E-2</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -628,15 +627,15 @@
         <v>-0.50822046631284201</v>
       </c>
       <c r="C12" s="3">
-        <v>4.0830035377452195E-2</v>
+        <v>4.06417606487008E-2</v>
       </c>
       <c r="D12" s="3">
-        <v>-0.52751216147522495</v>
+        <v>-0.52742667814849298</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -644,15 +643,15 @@
         <v>0.16135272889616398</v>
       </c>
       <c r="C13" s="3">
-        <v>0.132305179770425</v>
+        <v>0.13211100356955399</v>
       </c>
       <c r="D13" s="3">
-        <v>2.56534630810645E-2</v>
+        <v>2.5829380011686397E-2</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -660,15 +659,15 @@
         <v>4.2653898204950205E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-5.5893304990726506E-2</v>
+        <v>-5.21275025686933E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>0.10438142607887001</v>
+        <v>9.9993829371035792E-2</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -676,15 +675,15 @@
         <v>-8.1484893625715496E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>-5.5629924131158297E-2</v>
+        <v>-5.5969414178603197E-2</v>
       </c>
       <c r="D15" s="3">
-        <v>-2.7378005884790602E-2</v>
+        <v>-2.7028233862689398E-2</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -692,15 +691,15 @@
         <v>8.0414907331842894E-2</v>
       </c>
       <c r="C16" s="3">
-        <v>-4.6852851016192494E-3</v>
+        <v>-4.8679133106332897E-3</v>
       </c>
       <c r="D16" s="3">
-        <v>8.5500788001663094E-2</v>
+        <v>8.5700000817175506E-2</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -708,15 +707,15 @@
         <v>-2.8151510239368901E-2</v>
       </c>
       <c r="C17" s="3">
-        <v>6.2593007441142892E-2</v>
+        <v>6.1796114375139703E-2</v>
       </c>
       <c r="D17" s="3">
-        <v>-8.5399129342132604E-2</v>
+        <v>-8.4712708397357395E-2</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -724,15 +723,15 @@
         <v>0.43293044701734096</v>
       </c>
       <c r="C18" s="3">
-        <v>4.8573894277164499E-2</v>
+        <v>4.8059584097887402E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>0.36655170879028298</v>
+        <v>0.36722231136384204</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -740,15 +739,15 @@
         <v>-8.92960356707065E-2</v>
       </c>
       <c r="C19" s="3">
-        <v>5.4245720871528701E-2</v>
+        <v>5.3733888854991196E-2</v>
       </c>
       <c r="D19" s="3">
-        <v>-0.136155882542801</v>
+        <v>-0.13573628601915499</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -756,15 +755,15 @@
         <v>5.39905826262434E-2</v>
       </c>
       <c r="C20" s="3">
-        <v>0.20300206038631299</v>
+        <v>0.202723913506234</v>
       </c>
       <c r="D20" s="3">
-        <v>-0.12386635290734099</v>
+        <v>-0.123663734635821</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -772,15 +771,15 @@
         <v>0.26949149672343004</v>
       </c>
       <c r="C21" s="3">
-        <v>9.1453591743375404E-2</v>
+        <v>9.1796281643981903E-2</v>
       </c>
       <c r="D21" s="3">
-        <v>0.163119995505878</v>
+        <v>0.16275491872154199</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -788,15 +787,15 @@
         <v>0.11338613096387799</v>
       </c>
       <c r="C22" s="3">
-        <v>-7.1386812458196192E-4</v>
+        <v>-5.4190543865861797E-4</v>
       </c>
       <c r="D22" s="3">
-        <v>0.11418150962860101</v>
+        <v>0.11398980809949701</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -804,15 +803,15 @@
         <v>0.16350152297708898</v>
       </c>
       <c r="C23" s="3">
-        <v>0.16057306049954001</v>
+        <v>0.15943894038348799</v>
       </c>
       <c r="D23" s="3">
-        <v>2.52329006869067E-3</v>
+        <v>3.50392112262265E-3</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -820,15 +819,15 @@
         <v>4.1618075280279901E-2</v>
       </c>
       <c r="C24" s="3">
-        <v>4.6154430372250498E-2</v>
+        <v>4.5041388189657999E-2</v>
       </c>
       <c r="D24" s="3">
-        <v>-4.3362193575536799E-3</v>
+        <v>-3.27576778112925E-3</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -836,15 +835,15 @@
         <v>4.4756900061544203E-2</v>
       </c>
       <c r="C25" s="3">
-        <v>0.17419293880352898</v>
+        <v>0.17448093591650299</v>
       </c>
       <c r="D25" s="3">
-        <v>-0.11023404626660099</v>
+        <v>-0.11045222777816199</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -852,15 +851,15 @@
         <v>1.1811139583517401E-2</v>
       </c>
       <c r="C26" s="3">
-        <v>0.10974336102993901</v>
+        <v>0.10753261320610999</v>
       </c>
       <c r="D26" s="3">
-        <v>-8.8247629934485608E-2</v>
+        <v>-8.6427679403044314E-2</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -868,15 +867,15 @@
         <v>-3.5229071663161901E-2</v>
       </c>
       <c r="C27" s="3">
-        <v>3.9869777483312101E-2</v>
+        <v>4.0404630917779599E-2</v>
       </c>
       <c r="D27" s="3">
-        <v>-7.2219474757914001E-2</v>
+        <v>-7.2696430151624997E-2</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
@@ -898,17 +897,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="156efd3b4c34ab36c49a3cc1bad9b9a6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1c801130155331743e24030937d8c3da" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3825d4c36eddbd19ff5877cf568b1130">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20db92a579f18a3b40827b4b7272a8b7" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
     <xsd:import namespace="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
     <xsd:element name="properties">
@@ -1155,40 +1145,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
-    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C77810-B834-48E6-BFAF-4A4D27671E71}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FB0389E-65D9-4625-BBEA-6061CB90D608}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
-    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}"/>
 </file>